--- a/light_fight/Assets/Excels/MonsterClassConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterClassConfig.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">HPScale</t>
+    <t xml:space="preserve">HealthScale</t>
   </si>
   <si>
     <t xml:space="preserve">AttackScale</t>
@@ -178,7 +178,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -195,19 +195,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -474,7 +478,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.06"/>
@@ -489,7 +493,7 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -506,16 +510,16 @@
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F2" s="1" t="n">
@@ -526,19 +530,19 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -546,19 +550,19 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -566,19 +570,19 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -586,19 +590,19 @@
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -606,19 +610,19 @@
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -626,19 +630,19 @@
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -646,19 +650,19 @@
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -666,215 +670,215 @@
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="n">
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="n">
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="n">
+      <c r="E14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/light_fight/Assets/Excels/MonsterClassConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterClassConfig.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">AttackScale</t>
   </si>
   <si>
-    <t xml:space="preserve">CooldownIntervalScale</t>
+    <t xml:space="preserve">CooldownScale</t>
   </si>
   <si>
     <t xml:space="preserve">SpeedScale</t>
@@ -480,7 +480,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.06"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="1" max="7" min="7" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
